--- a/results/05-2026/no_obbba_medicaid/beta/contributions-05-2026.xlsx
+++ b/results/05-2026/no_obbba_medicaid/beta/contributions-05-2026.xlsx
@@ -3036,7 +3036,7 @@
         <v>-0.0000531438557844164</v>
       </c>
       <c r="W25" t="n">
-        <v>-2.46516541780743</v>
+        <v>0.338301811894314</v>
       </c>
       <c r="X25" t="n">
         <v>0.0427711776553399</v>
@@ -3051,22 +3051,22 @@
         <v>-0.270169588737866</v>
       </c>
       <c r="AB25" t="n">
-        <v>-2.3929143019204</v>
+        <v>0.408480143900867</v>
       </c>
       <c r="AC25" t="n">
-        <v>-2.669863485065</v>
+        <v>0.139473515989945</v>
       </c>
       <c r="AD25" t="n">
         <v>-0.412652726526158</v>
       </c>
       <c r="AE25" t="n">
-        <v>-2.36864968944274</v>
+        <v>0.432744756378526</v>
       </c>
       <c r="AF25" t="n">
-        <v>-3.98760614783859</v>
+        <v>-1.17826914678364</v>
       </c>
       <c r="AG25" t="n">
-        <v>-1.19319839194488</v>
+        <v>-0.49086414168114</v>
       </c>
     </row>
     <row r="26">
@@ -3137,7 +3137,7 @@
         <v>-0.0000696617484409661</v>
       </c>
       <c r="W26" t="n">
-        <v>-2.57824559230892</v>
+        <v>0.279329039690738</v>
       </c>
       <c r="X26" t="n">
         <v>0.0124692193307716</v>
@@ -3152,22 +3152,22 @@
         <v>0.463404670727734</v>
       </c>
       <c r="AB26" t="n">
-        <v>-2.87066837584301</v>
+        <v>-0.00467134528318946</v>
       </c>
       <c r="AC26" t="n">
-        <v>-2.33349332501075</v>
+        <v>0.518755843342824</v>
       </c>
       <c r="AD26" t="n">
         <v>0.148888893636348</v>
       </c>
       <c r="AE26" t="n">
-        <v>-2.86941545840702</v>
+        <v>-0.00341842784719892</v>
       </c>
       <c r="AF26" t="n">
-        <v>-1.9680428459692</v>
+        <v>0.884206322384365</v>
       </c>
       <c r="AG26" t="n">
-        <v>-1.51889264816751</v>
+        <v>-0.103496105815382</v>
       </c>
     </row>
     <row r="27">
@@ -3238,7 +3238,7 @@
         <v>-0.000501429966115183</v>
       </c>
       <c r="W27" t="n">
-        <v>0.314277308220622</v>
+        <v>0.247504863679855</v>
       </c>
       <c r="X27" t="n">
         <v>0.0487650643212487</v>
@@ -3253,22 +3253,22 @@
         <v>0.485607963229528</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.108609652803962</v>
+        <v>0.0416926751894501</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.653664131653691</v>
+        <v>0.587088193681598</v>
       </c>
       <c r="AD27" t="n">
         <v>0.234064323299038</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.111693310324959</v>
+        <v>0.0447763327104476</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.230235252248326</v>
+        <v>0.163659314276233</v>
       </c>
       <c r="AG27" t="n">
-        <v>-1.35885841965417</v>
+        <v>0.0398941382049361</v>
       </c>
     </row>
     <row r="28">
@@ -3339,7 +3339,7 @@
         <v>-0.000426940925803921</v>
       </c>
       <c r="W28" t="n">
-        <v>0.265294689286821</v>
+        <v>0.200762093320125</v>
       </c>
       <c r="X28" t="n">
         <v>-0.0141682460370789</v>
@@ -3354,22 +3354,22 @@
         <v>0.255014185511323</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.192741327130953</v>
+        <v>0.128159277609808</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.507237755330661</v>
+        <v>0.442829230353156</v>
       </c>
       <c r="AD28" t="n">
         <v>0.177083575542115</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.188480687257591</v>
+        <v>0.123898637736446</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.184658419292605</v>
+        <v>0.120249894315099</v>
       </c>
       <c r="AG28" t="n">
-        <v>-1.38518883056672</v>
+        <v>-0.00253840395198553</v>
       </c>
     </row>
     <row r="29">
@@ -3440,7 +3440,7 @@
         <v>-0.000395175505607586</v>
       </c>
       <c r="W29" t="n">
-        <v>2.81612295301479</v>
+        <v>0.164055586793484</v>
       </c>
       <c r="X29" t="n">
         <v>0.0153627081459999</v>
@@ -3455,22 +3455,22 @@
         <v>-0.0600454191026175</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.83142841196469</v>
+        <v>0.17980531124795</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.83318744300148</v>
+        <v>0.179873938990407</v>
       </c>
       <c r="AD29" t="n">
         <v>-0.00775380490190472</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.82279685974376</v>
+        <v>0.171173759027019</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.52636476622369</v>
+        <v>-0.126948737787385</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.243303897948853</v>
+        <v>0.260291698297078</v>
       </c>
     </row>
     <row r="30">
@@ -3541,7 +3541,7 @@
         <v>-0.000365697253103981</v>
       </c>
       <c r="W30" t="n">
-        <v>2.80687638466247</v>
+        <v>0.125233288715792</v>
       </c>
       <c r="X30" t="n">
         <v>0.0224941043379145</v>
@@ -3556,22 +3556,22 @@
         <v>-0.533901846857373</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.94241054209427</v>
+        <v>0.264760058414852</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.48523060067817</v>
+        <v>-0.207644369916542</v>
       </c>
       <c r="AD30" t="n">
         <v>-0.267027899335481</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.94003632056022</v>
+        <v>0.262385836880811</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.18504030839429</v>
+        <v>-0.50783466220042</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.28157468653973</v>
+        <v>-0.0877185478491185</v>
       </c>
     </row>
     <row r="31">
@@ -3672,7 +3672,7 @@
         <v>-0.559156015161296</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.08422686968732</v>
+        <v>-0.268422380208501</v>
       </c>
     </row>
     <row r="32">
@@ -3773,7 +3773,7 @@
         <v>-0.472147349836769</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.920025427404978</v>
+        <v>-0.416521691246468</v>
       </c>
     </row>
     <row r="33">
@@ -3874,7 +3874,7 @@
         <v>-0.579968253346469</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.143442172512439</v>
+        <v>-0.529776570136239</v>
       </c>
     </row>
     <row r="34">
